--- a/crates/core/tests/fixtures/m2/Text.xlsx
+++ b/crates/core/tests/fixtures/m2/Text.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="514">
   <si>
     <t>Description</t>
   </si>
@@ -725,18 +725,54 @@
     <t>=PROPER("john's car")</t>
   </si>
   <si>
-    <t>numbers ignored</t>
+    <t>numbers ignored: hello2world</t>
   </si>
   <si>
     <t>=PROPER("hello2world")</t>
   </si>
   <si>
-    <t>already proper case</t>
+    <t>already proper case unchanged</t>
   </si>
   <si>
     <t>=PROPER("Hello World")</t>
   </si>
   <si>
+    <t>leading spaces preserved</t>
+  </si>
+  <si>
+    <t>=PROPER("  hello world")</t>
+  </si>
+  <si>
+    <t>hyphenated name: mary-ann</t>
+  </si>
+  <si>
+    <t>=PROPER("mary-ann")</t>
+  </si>
+  <si>
+    <t>coercion: number 123 -&gt; "123"</t>
+  </si>
+  <si>
+    <t>=PROPER(123)</t>
+  </si>
+  <si>
+    <t>coercion: TRUE -&gt; "True"</t>
+  </si>
+  <si>
+    <t>=PROPER(TRUE)</t>
+  </si>
+  <si>
+    <t>coercion: FALSE -&gt; "False"</t>
+  </si>
+  <si>
+    <t>=PROPER(FALSE)</t>
+  </si>
+  <si>
+    <t>error propagation: PROPER(1/0) -&gt; #DIV/0!</t>
+  </si>
+  <si>
+    <t>=PROPER(1/0)</t>
+  </si>
+  <si>
     <t>=PROPER()</t>
   </si>
   <si>
@@ -746,6 +782,18 @@
     <t>=PROPER(LOWER("HELLO"))</t>
   </si>
   <si>
+    <t>nested: PROPER(CONCATENATE("hello"," ","world"))</t>
+  </si>
+  <si>
+    <t>=PROPER(CONCATENATE("hello"," ","world"))</t>
+  </si>
+  <si>
+    <t>nested: LEN(PROPER("hello world"))</t>
+  </si>
+  <si>
+    <t>=LEN(PROPER("hello world"))</t>
+  </si>
+  <si>
     <t>digits from foo123bar</t>
   </si>
   <si>
@@ -1151,15 +1199,45 @@
     <t>=SEARCH("h","Hello")</t>
   </si>
   <si>
-    <t>start from 2</t>
+    <t>start from 4 finds l at 4</t>
   </si>
   <si>
     <t>=SEARCH("l","Hello",4)</t>
   </si>
   <si>
+    <t>? wildcard single char W?rld -&gt; 7</t>
+  </si>
+  <si>
+    <t>=SEARCH("W?rld","Hello World")</t>
+  </si>
+  <si>
+    <t>* wildcard trailing *orld -&gt; 7</t>
+  </si>
+  <si>
+    <t>=SEARCH("*orld","Hello World")</t>
+  </si>
+  <si>
+    <t>start pos equals length</t>
+  </si>
+  <si>
+    <t>=SEARCH("d","World",5)</t>
+  </si>
+  <si>
+    <t>coercion: find number in string</t>
+  </si>
+  <si>
+    <t>=SEARCH("2","abc123")</t>
+  </si>
+  <si>
     <t>=SEARCH("z","Hello")</t>
   </si>
   <si>
+    <t>error: start pos out of range -&gt; #VALUE!</t>
+  </si>
+  <si>
+    <t>=SEARCH("o","Hello",100)</t>
+  </si>
+  <si>
     <t>=SEARCH()</t>
   </si>
   <si>
@@ -1167,6 +1245,18 @@
   </si>
   <si>
     <t>=MID("Hello World",SEARCH(" ","Hello World")+1,5)</t>
+  </si>
+  <si>
+    <t>nested: LEN minus SEARCH for suffix length</t>
+  </si>
+  <si>
+    <t>=LEN("Hello World")-SEARCH(" ","Hello World")</t>
+  </si>
+  <si>
+    <t>nested: SEARCH inside IF</t>
+  </si>
+  <si>
+    <t>=IF(ISNUMBER(SEARCH("World","Hello World")),"found","not found")</t>
   </si>
   <si>
     <t>world case-insensitive -&gt; 7</t>
@@ -2467,10 +2557,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.25"/>
-    <col customWidth="1" min="2" max="2" width="21.38"/>
+    <col customWidth="1" min="1" max="1" width="37.5"/>
+    <col customWidth="1" min="2" max="2" width="32.75"/>
     <col customWidth="1" min="3" max="3" width="14.13"/>
-    <col customWidth="1" min="4" max="4" width="5.88"/>
+    <col customWidth="1" min="4" max="4" width="7.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2608,32 +2698,152 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <f>PROPER("  hello world")</f>
+        <v>  Hello World</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f>PROPER("mary-ann")</f>
+        <v>Mary-Ann</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="13" t="str">
+        <f>PROPER(123)</f>
+        <v>123</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="13" t="str">
+        <f>PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="13" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f>PROPER(1/0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="7" t="str">
+      <c r="B16" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="7" t="str">
         <f>PROPER()</f>
         <v>#N/A</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="10" t="str">
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="10" t="str">
         <f>PROPER(LOWER("HELLO"))</f>
         <v>Hello</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D17" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="10" t="str">
+        <f>PROPER(CONCATENATE("hello"," ","world"))</f>
+        <v>Hello World</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="10">
+        <f>LEN(PROPER("hello world"))</f>
+        <v>11</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2671,10 +2881,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""foo123bar"",""[0-9]+"")"),"123")</f>
@@ -2686,10 +2896,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""hello@world.com"",""@[^.]+"")"),"@world")</f>
@@ -2701,10 +2911,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""2024-01-15"",""[0-9]{4}"")"),"2024")</f>
@@ -2716,10 +2926,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""abc"",""[a-z]+"")"),"abc")</f>
@@ -2731,10 +2941,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""hello world"",""[a-z]+"")"),"hello")</f>
@@ -2746,10 +2956,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""a1b2"",""[0-9]"")"),"1")</f>
@@ -2761,10 +2971,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""2024-01-15"",""([0-9]{4})-([0-9]{2})"")"),"#REF!")</f>
@@ -2776,10 +2986,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT(""hello"",""[0-9]+"")"),"#N/A")</f>
@@ -2794,7 +3004,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXEXTRACT()"),"#N/A")</f>
@@ -2806,10 +3016,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C11" s="10">
         <f>IFERROR(__xludf.DUMMYFUNCTION("LEN(REGEXEXTRACT(""foo123"",""[0-9]+""))"),3.0)</f>
@@ -2853,10 +3063,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="C2" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""hello123"",""[0-9]+"")"),TRUE)</f>
@@ -2868,10 +3078,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C3" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""hello"",""[0-9]+"")"),FALSE)</f>
@@ -2883,10 +3093,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="C4" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""test@email.com"",""@"")"),TRUE)</f>
@@ -2898,10 +3108,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C5" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""abc"",""^abc$"")"),TRUE)</f>
@@ -2913,10 +3123,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="C6" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""abcd"",""^abc$"")"),FALSE)</f>
@@ -2928,10 +3138,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="C7" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH("""",""."")"),FALSE)</f>
@@ -2943,10 +3153,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="C8" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""x"",""."")"),TRUE)</f>
@@ -2958,10 +3168,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C9" s="4" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH(""abc"",""^xyz"")"),FALSE)</f>
@@ -2976,7 +3186,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXMATCH()"),"#N/A")</f>
@@ -2988,10 +3198,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(REGEXMATCH(""abc123"",""[0-9]+""),""yes"",""no"")"),"yes")</f>
@@ -3035,10 +3245,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(""foo123bar"",""[0-9]+"",""NUM"")"),"fooNUMbar")</f>
@@ -3050,10 +3260,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(""hello world"","" "",""-"")"),"hello-world")</f>
@@ -3065,10 +3275,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(""aabbcc"",""b+"",""X"")"),"aaXcc")</f>
@@ -3080,10 +3290,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(""no match"",""[0-9]+"",""X"")"),"no match")</f>
@@ -3098,7 +3308,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE("""",""a"",""b"")"),"")</f>
@@ -3110,10 +3320,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(""hello"",""[aeiou]"",""*"")"),"h*ll*")</f>
@@ -3125,10 +3335,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(""abc"",""^"",""X"")"),"Xabc")</f>
@@ -3143,7 +3353,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE()"),"#N/A")</f>
@@ -3155,10 +3365,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C10" s="10">
         <f>IFERROR(__xludf.DUMMYFUNCTION("LEN(REGEXREPLACE(""hello world"","" "",""""))"),10.0)</f>
@@ -3170,10 +3380,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("UPPER(REGEXREPLACE(""foo123"",""[0-9]+"",""""))"),"FOO")</f>
@@ -3217,10 +3427,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>REPLACE("Hello World",7,5,"Earth")</f>
@@ -3232,10 +3442,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>REPLACE("abcdef",3,2,"XX")</f>
@@ -3247,10 +3457,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>REPLACE("Hello",1,5,"Bye")</f>
@@ -3262,10 +3472,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>REPLACE("Hello",3,0,"!!!")</f>
@@ -3277,10 +3487,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>REPLACE("Hello",6,0,"!")</f>
@@ -3292,10 +3502,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>REPLACE("abc",1,0,"Z")</f>
@@ -3307,10 +3517,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>REPLACE("ab",5,0,"cd")</f>
@@ -3325,7 +3535,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>REPLACE()</f>
@@ -3337,10 +3547,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="C10" s="10">
         <f>LEN(REPLACE("Hello",1,5,"Hi"))</f>
@@ -3352,10 +3562,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>UPPER(REPLACE("hello",1,1,"H"))</f>
@@ -3399,10 +3609,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>REPLACEB("Hello World",7,5,"Earth")</f>
@@ -3414,10 +3624,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>REPLACEB("abc",2,1,"X")</f>
@@ -3429,10 +3639,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>REPLACEB("Hello",1,1,"J")</f>
@@ -3444,10 +3654,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>REPLACEB("Hi",1,2,"OK")</f>
@@ -3459,10 +3669,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>REPLACEB("abc",1,0,"Z")</f>
@@ -3474,10 +3684,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>REPLACEB("ab",3,0,"cd")</f>
@@ -3489,10 +3699,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>REPLACEB("Hello",1,3,"")</f>
@@ -3507,7 +3717,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>REPLACEB()</f>
@@ -3519,10 +3729,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="C10" s="10" t="b">
         <f>REPLACEB("abc",2,1,"X")=REPLACE("abc",2,1,"X")</f>
@@ -3534,10 +3744,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="C11" s="10">
         <f>LEN(REPLACEB("abc",2,1,"XX"))</f>
@@ -3581,10 +3791,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>RIGHTB("Hello",3)</f>
@@ -3599,7 +3809,7 @@
         <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>RIGHTB("Hello",5)</f>
@@ -3614,7 +3824,7 @@
         <v>163</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>RIGHTB("Hello",0)</f>
@@ -3629,7 +3839,7 @@
         <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>RIGHTB("",3)</f>
@@ -3644,7 +3854,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>RIGHTB("Hello",1)</f>
@@ -3656,10 +3866,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>RIGHTB("abc",3)</f>
@@ -3674,7 +3884,7 @@
         <v>171</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>RIGHTB("Hi",10)</f>
@@ -3689,7 +3899,7 @@
         <v>173</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>RIGHTB("Hello",-1)</f>
@@ -3704,7 +3914,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>RIGHTB()</f>
@@ -3716,10 +3926,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="C11" s="10">
         <f>LEN(RIGHTB("Hello",3))</f>
@@ -3763,10 +3973,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>ROMAN(14)</f>
@@ -3778,10 +3988,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>ROMAN(1999)</f>
@@ -3793,10 +4003,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>ROMAN(1)</f>
@@ -3808,10 +4018,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>ROMAN(4)</f>
@@ -3823,10 +4033,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>ROMAN(3999)</f>
@@ -3838,10 +4048,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>ROMAN(0)</f>
@@ -3853,10 +4063,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>ROMAN(400)</f>
@@ -3871,7 +4081,7 @@
         <v>173</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>ROMAN(-1)</f>
@@ -3883,10 +4093,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>ROMAN(4000)</f>
@@ -3901,7 +4111,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="C11" s="7" t="str">
         <f>ROMAN()</f>
@@ -3913,10 +4123,10 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C12" s="10">
         <f>ARABIC(ROMAN(99))</f>
@@ -4120,10 +4330,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.38"/>
-    <col customWidth="1" min="2" max="2" width="36.88"/>
+    <col customWidth="1" min="1" max="1" width="32.75"/>
+    <col customWidth="1" min="2" max="2" width="49.13"/>
     <col customWidth="1" min="3" max="3" width="14.13"/>
-    <col customWidth="1" min="4" max="4" width="5.88"/>
+    <col customWidth="1" min="4" max="4" width="7.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,7 +4355,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C2" s="4">
         <f>SEARCH("o","Hello World")</f>
@@ -4157,10 +4367,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="C3" s="4">
         <f>SEARCH("WORLD","Hello World")</f>
@@ -4172,10 +4382,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="C4" s="4">
         <f>SEARCH("h?llo","Hello World")</f>
@@ -4187,10 +4397,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C5" s="4">
         <f>SEARCH("h*o","Hello World")</f>
@@ -4205,7 +4415,7 @@
         <v>95</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="C6" s="4">
         <f>SEARCH("o","Hello World",6)</f>
@@ -4217,10 +4427,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="C7" s="4">
         <f>SEARCH("h","Hello")</f>
@@ -4232,10 +4442,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C8" s="4">
         <f>SEARCH("l","Hello",4)</f>
@@ -4246,47 +4456,152 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" s="4">
+        <f>SEARCH("W?rld","Hello World")</f>
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C10" s="4">
+        <f>SEARCH("*orld","Hello World")</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" s="4">
+        <f>SEARCH("d","World",5)</f>
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="C12" s="13">
+        <f>SEARCH("2","abc123")</f>
+        <v>5</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C9" s="7" t="str">
+      <c r="B13" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C13" s="7" t="str">
         <f>SEARCH("z","Hello")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f>SEARCH("o","Hello",100)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="C10" s="7" t="str">
+      <c r="B15" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" s="7" t="str">
         <f>SEARCH()</f>
         <v>#N/A</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="C11" s="10" t="str">
+    <row r="16">
+      <c r="A16" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" s="10" t="str">
         <f>MID("Hello World",SEARCH(" ","Hello World")+1,5)</f>
         <v>World</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D16" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C17" s="10">
+        <f>LEN("Hello World")-SEARCH(" ","Hello World")</f>
+        <v>5</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="C18" s="10" t="str">
+        <f>IF(ISNUMBER(SEARCH("World","Hello World")),"found","not found")</f>
+        <v>found</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4324,10 +4639,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="C2" s="4">
         <f>SEARCHB("world","Hello World")</f>
@@ -4342,7 +4657,7 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="C3" s="4">
         <f>SEARCHB("H","Hello World")</f>
@@ -4354,10 +4669,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="C4" s="4">
         <f>SEARCHB("HELLO","Hello")</f>
@@ -4372,7 +4687,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="C5" s="4">
         <f>SEARCHB("l","Hello")</f>
@@ -4384,10 +4699,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="C6" s="4">
         <f>SEARCHB("l","Hello",4)</f>
@@ -4402,7 +4717,7 @@
         <v>97</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="C7" s="4">
         <f>SEARCHB("","Hello")</f>
@@ -4417,7 +4732,7 @@
         <v>103</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="C8" s="7" t="str">
         <f>SEARCHB("z","Hello")</f>
@@ -4432,7 +4747,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>SEARCHB()</f>
@@ -4444,10 +4759,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="C10" s="10" t="b">
         <f>SEARCHB("world","Hello World")=SEARCH("world","Hello World")</f>
@@ -4459,10 +4774,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>MID("Hello World",SEARCHB(" ","Hello World")+1,5)</f>
@@ -4506,10 +4821,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(SPLIT(""a,b,c"","",""),1)"),"a")</f>
@@ -4521,10 +4836,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(SPLIT(""a,b,c"","",""),2)"),"b")</f>
@@ -4536,10 +4851,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(SPLIT(""a,b,c"","",""),3)"),"c")</f>
@@ -4551,10 +4866,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="C5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(SPLIT(""a,b,c"","",""))"),3.0)</f>
@@ -4566,10 +4881,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="C6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(SPLIT(""hello world"","" ""))"),2.0)</f>
@@ -4581,10 +4896,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
       <c r="C7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(SPLIT(""a,,b"","","",TRUE,TRUE))"),2.0)</f>
@@ -4596,10 +4911,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="C8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(SPLIT(""a,,b"","","",TRUE,FALSE))"),2.0)</f>
@@ -4611,10 +4926,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="C9" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(SPLIT(""hello"","",""),1)"),"hello")</f>
@@ -4629,7 +4944,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SPLIT()"),"#N/A")</f>
@@ -4641,10 +4956,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="C11" s="10">
         <f>IFERROR(__xludf.DUMMYFUNCTION("LEN(INDEX(SPLIT(""hello world"","" ""),1))"),5.0)</f>
@@ -4688,10 +5003,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>SUBSTITUTE("Hello World","World","Earth")</f>
@@ -4703,10 +5018,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>SUBSTITUTE("aabbaa","a","X")</f>
@@ -4718,10 +5033,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>SUBSTITUTE("aabbaa","a","X",1)</f>
@@ -4733,10 +5048,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>SUBSTITUTE("aabbaa","a","X",2)</f>
@@ -4748,10 +5063,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>SUBSTITUTE("Hello","z","X")</f>
@@ -4766,7 +5081,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>SUBSTITUTE("","a","b")</f>
@@ -4778,10 +5093,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>SUBSTITUTE("hello","l","")</f>
@@ -4793,10 +5108,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="C9" s="4" t="str">
         <f>SUBSTITUTE("aaaa","a","X",3)</f>
@@ -4811,7 +5126,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>SUBSTITUTE()</f>
@@ -4823,10 +5138,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="C11" s="10">
         <f>LEN(SUBSTITUTE("hello","l",""))</f>
@@ -4870,10 +5185,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>TEXT(1234.567,"#,##0.00")</f>
@@ -4885,10 +5200,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>TEXT(0.5,"0%")</f>
@@ -4900,10 +5215,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>TEXT(DATE(2024,1,15),"yyyy-mm-dd")</f>
@@ -4915,10 +5230,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>TEXT(42,"00000")</f>
@@ -4930,10 +5245,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>TEXT(-42,"#,##0")</f>
@@ -4945,10 +5260,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>TEXT(0,"0.00")</f>
@@ -4960,10 +5275,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>TEXT(1000000,"#,##0")</f>
@@ -4975,10 +5290,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="C9" s="4" t="str">
         <f>TEXT(0.25,"0/4")</f>
@@ -4993,7 +5308,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>TEXT()</f>
@@ -5005,10 +5320,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="C11" s="10">
         <f>LEN(TEXT(1000,"#,##0"))</f>
@@ -5052,10 +5367,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>TEXTJOIN(",",TRUE,"a","b","c")</f>
@@ -5067,10 +5382,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>TEXTJOIN(",",TRUE,"a","","c")</f>
@@ -5082,10 +5397,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>TEXTJOIN(",",FALSE,"a","","c")</f>
@@ -5097,10 +5412,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="C5" s="4" t="str">
         <f t="array" ref="C5">TEXTJOIN("-",TRUE,{1,2,3})</f>
@@ -5115,7 +5430,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>TEXTJOIN("",TRUE,"Hello"," ","World")</f>
@@ -5130,7 +5445,7 @@
         <v>148</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>TEXTJOIN(",",TRUE,"only")</f>
@@ -5142,10 +5457,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>TEXTJOIN(",",TRUE,"","","")</f>
@@ -5160,7 +5475,7 @@
         <v>150</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="C9" s="4" t="str">
         <f>TEXTJOIN("|",TRUE,"x","y","z")</f>
@@ -5175,7 +5490,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>TEXTJOIN()</f>
@@ -5187,10 +5502,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="C11" s="10">
         <f>LEN(TEXTJOIN(",",TRUE,"a","b","c"))</f>
@@ -5234,10 +5549,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="C2" s="4">
         <f>VALUE("42")</f>
@@ -5249,10 +5564,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="C3" s="4">
         <f>VALUE("3.14")</f>
@@ -5264,10 +5579,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="C4" s="4">
         <f>VALUE("-5")</f>
@@ -5279,10 +5594,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C5" s="4">
         <f>VALUE("0")</f>
@@ -5294,10 +5609,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="C6" s="4">
         <f>VALUE("1.5e3")</f>
@@ -5309,10 +5624,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="C7" s="4">
         <f>VALUE("007")</f>
@@ -5324,10 +5639,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="C8" s="4">
         <f>VALUE(".5")</f>
@@ -5339,10 +5654,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>VALUE("abc")</f>
@@ -5354,10 +5669,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="C10" s="7">
         <f>VALUE("")</f>
@@ -5372,7 +5687,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="C11" s="7" t="str">
         <f>VALUE()</f>
@@ -5384,10 +5699,10 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="C12" s="10">
         <f>VALUE(TEXT(42,"0"))</f>
